--- a/data/fixtures/obldiagcentr_shymkent.xlsx
+++ b/data/fixtures/obldiagcentr_shymkent.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -449,24 +449,24 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>УЗИ брюшной полости</t>
+          <t>гастроскопия</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7 650 ₸</t>
+          <t>10 800 ₸</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>УЗИ малого таза</t>
+          <t>Колоноскопия</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7 200 ₸</t>
+          <t>16 200 ₸</t>
         </is>
       </c>
     </row>
@@ -485,163 +485,163 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>УЗИ молочных желёз</t>
+          <t>МРТ головного мозга</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6 300 ₸</t>
+          <t>25 200 ₸</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ЭхоКГ</t>
+          <t>МРТ пояснично-крестцового отдела</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>9 900 ₸</t>
+          <t>23 400 ₸</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ЭКГ с расшифровкой</t>
+          <t>ультразвуковое исследование брюшной полости</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3 150 ₸</t>
+          <t>7 650 ₸</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>флюорография</t>
+          <t>УЗИ МЖ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2 250 ₸</t>
+          <t>6 300 ₸</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>МРТ пояснично-крестцового отдела</t>
+          <t>УЗИ органов малого таза</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23 400 ₸</t>
+          <t>7 200 ₸</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>компьютерная томография ОГК</t>
+          <t>УЗИ почек</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21 600 ₸</t>
+          <t>5 850 ₸</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Колоноскопия</t>
+          <t>рентгенография органов грудной клетки</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16 200 ₸</t>
+          <t>4 050 ₸</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Холтеровское мониторирование ЭКГ</t>
+          <t>3D УЗИ плода</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8 100 ₸</t>
+          <t>7 650 ₸</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>клинический анализ крови</t>
+          <t>УЗИ при беременности 1 триместра</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2 000 ₸</t>
+          <t>7 550 ₸</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>общеклинический анализ мочи</t>
+          <t>КТ голеностопного сустава</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1 350 ₸</t>
+          <t>20 700 ₸</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Глюкоза крови</t>
+          <t>ангиография</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1 150 ₸</t>
+          <t>27 500 ₸</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>гликозилированный гемоглобин</t>
+          <t>ОАМ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3 800 ₸</t>
+          <t>1 350 ₸</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>холестерин</t>
+          <t>HbA1c</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1 250 ₸</t>
+          <t>3 800 ₸</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>АсАТ</t>
+          <t>Билирубин общий</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -653,79 +653,79 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>креатинин в крови</t>
+          <t>ферритин</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1 150 ₸</t>
+          <t>3 850 ₸</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Коагулограмма</t>
+          <t>Холестерин</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4 850 ₸</t>
+          <t>1 250 ₸</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>С-реактивный белок (СРБ)</t>
+          <t>Мочевина</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2 350 ₸</t>
+          <t>1 150 ₸</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>тиротропин</t>
+          <t>креатинин в крови</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2 800 ₸</t>
+          <t>1 150 ₸</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>тироксин свободный</t>
+          <t>Витамин D</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2 800 ₸</t>
+          <t>8 000 ₸</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ferritin</t>
+          <t>HBsAg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3 850 ₸</t>
+          <t>2 500 ₸</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>витамин В12</t>
+          <t>Витамин B12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -737,96 +737,72 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>антитела к ковид</t>
+          <t>ПСА общий</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4 700 ₸</t>
+          <t>3 250 ₸</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>гепатит С</t>
+          <t>Пролактин</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2 700 ₸</t>
+          <t>2 950 ₸</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PSA</t>
+          <t>тестостерон</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3 250 ₸</t>
+          <t>2 950 ₸</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>prolactin</t>
+          <t>TSH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2 950 ₸</t>
+          <t>2 800 ₸</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>группа крови и резус</t>
+          <t>IgG к коронавирусу</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2 150 ₸</t>
+          <t>4 700 ₸</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>D-dimer</t>
+          <t>Резус-фактор</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4 850 ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>гинекологический мазок</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2 050 ₸</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Спермограмма</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>6 500 ₸</t>
+          <t>2 150 ₸</t>
         </is>
       </c>
     </row>
